--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008472774029021725</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>51893867</v>
+        <v>3962659</v>
       </c>
       <c r="L2" t="n">
-        <v>26396702</v>
+        <v>1524001</v>
       </c>
       <c r="M2" t="n">
-        <v>6192170</v>
+        <v>309449</v>
       </c>
       <c r="N2" t="n">
-        <v>229794</v>
+        <v>6226</v>
       </c>
       <c r="O2" t="n">
-        <v>3613783</v>
+        <v>171667</v>
       </c>
       <c r="P2" t="n">
-        <v>1304941</v>
+        <v>3331</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999911904335022</v>
+        <v>0.9999353885650635</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8184267282485962</v>
+        <v>0.6990041732788086</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6928279995918274</v>
+        <v>0.522357702255249</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6036193370819092</v>
+        <v>0.3773676156997681</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1807366460561752</v>
+        <v>0.03851626440882683</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6544100046157837</v>
+        <v>0.3876615464687347</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7986351251602173</v>
+        <v>0.6440448760986328</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002031055628665047</v>
       </c>
       <c r="C3" t="n">
-        <v>4099</v>
+        <v>273</v>
       </c>
       <c r="D3" t="n">
-        <v>51893867</v>
+        <v>3962659</v>
       </c>
       <c r="E3" t="n">
-        <v>7718271</v>
+        <v>897888</v>
       </c>
       <c r="F3" t="n">
-        <v>285873</v>
+        <v>56617</v>
       </c>
       <c r="G3" t="n">
-        <v>23359</v>
+        <v>5434</v>
       </c>
       <c r="H3" t="n">
-        <v>21958</v>
+        <v>5612</v>
       </c>
       <c r="I3" t="n">
-        <v>779</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>120192788</v>
+        <v>10016214</v>
       </c>
       <c r="K3" t="n">
-        <v>124494004</v>
+        <v>9694743</v>
       </c>
       <c r="L3" t="n">
-        <v>144764664</v>
+        <v>11590590</v>
       </c>
       <c r="M3" t="n">
-        <v>180647128</v>
+        <v>14873498</v>
       </c>
       <c r="N3" t="n">
-        <v>193839971</v>
+        <v>16084111</v>
       </c>
       <c r="O3" t="n">
-        <v>187920856</v>
+        <v>15545446</v>
       </c>
       <c r="P3" t="n">
-        <v>193303582</v>
+        <v>16133709</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8656450510025024</v>
+        <v>0.804027795791626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6684858202934265</v>
+        <v>0.4555419385433197</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5508146286010742</v>
+        <v>0.3272753655910492</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2140420079231262</v>
+        <v>0.06912478059530258</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5899161100387573</v>
+        <v>0.3346374332904816</v>
       </c>
       <c r="W3" t="n">
-        <v>0.561846137046814</v>
+        <v>0.01716567948460579</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03202893469858889</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>10516217</v>
+        <v>1505205</v>
       </c>
       <c r="E4" t="n">
-        <v>26396702</v>
+        <v>1524001</v>
       </c>
       <c r="F4" t="n">
-        <v>2163340</v>
+        <v>248633</v>
       </c>
       <c r="G4" t="n">
-        <v>146246</v>
+        <v>27533</v>
       </c>
       <c r="H4" t="n">
-        <v>247504</v>
+        <v>39877</v>
       </c>
       <c r="I4" t="n">
-        <v>17283</v>
+        <v>219</v>
       </c>
       <c r="J4" t="n">
-        <v>6676</v>
+        <v>408</v>
       </c>
       <c r="K4" t="n">
-        <v>11512990</v>
+        <v>1706347</v>
       </c>
       <c r="L4" t="n">
-        <v>11703233</v>
+        <v>1393542</v>
       </c>
       <c r="M4" t="n">
-        <v>4066232</v>
+        <v>510571</v>
       </c>
       <c r="N4" t="n">
-        <v>1041636</v>
+        <v>155420</v>
       </c>
       <c r="O4" t="n">
-        <v>1908417</v>
+        <v>271160</v>
       </c>
       <c r="P4" t="n">
-        <v>329023</v>
+        <v>1841</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999955952167511</v>
+        <v>0.9999676942825317</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8413739800453186</v>
+        <v>0.747846782207489</v>
       </c>
       <c r="S4" t="n">
-        <v>0.680439293384552</v>
+        <v>0.4866671860218048</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5760093331336975</v>
+        <v>0.3505409955978394</v>
       </c>
       <c r="U4" t="n">
-        <v>0.195984423160553</v>
+        <v>0.04946864768862724</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6204916834831238</v>
+        <v>0.3592032492160797</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6596342921257019</v>
+        <v>0.03344008326530457</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1892</v>
+        <v>126</v>
       </c>
       <c r="D5" t="n">
-        <v>715182</v>
+        <v>147587</v>
       </c>
       <c r="E5" t="n">
-        <v>3181503</v>
+        <v>360580</v>
       </c>
       <c r="F5" t="n">
-        <v>6192170</v>
+        <v>309449</v>
       </c>
       <c r="G5" t="n">
-        <v>324769</v>
+        <v>41630</v>
       </c>
       <c r="H5" t="n">
-        <v>757626</v>
+        <v>85717</v>
       </c>
       <c r="I5" t="n">
-        <v>68698</v>
+        <v>442</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8054339</v>
+        <v>965851</v>
       </c>
       <c r="L5" t="n">
-        <v>13090601</v>
+        <v>1821467</v>
       </c>
       <c r="M5" t="n">
-        <v>5049670</v>
+        <v>636082</v>
       </c>
       <c r="N5" t="n">
-        <v>843799</v>
+        <v>83843</v>
       </c>
       <c r="O5" t="n">
-        <v>2512144</v>
+        <v>341327</v>
       </c>
       <c r="P5" t="n">
-        <v>1017654</v>
+        <v>190719</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999659061431885</v>
+        <v>0.9999750256538391</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9001438617706299</v>
+        <v>0.8363586664199829</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8734719157218933</v>
+        <v>0.8031176924705505</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9534796476364136</v>
+        <v>0.9297807216644287</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9903782606124878</v>
+        <v>0.9853478670120239</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9774409532546997</v>
+        <v>0.9624922275543213</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931276440620422</v>
+        <v>0.9882079362869263</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>323</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>193976</v>
+        <v>25629</v>
       </c>
       <c r="E6" t="n">
-        <v>248118</v>
+        <v>25085</v>
       </c>
       <c r="F6" t="n">
-        <v>275708</v>
+        <v>24351</v>
       </c>
       <c r="G6" t="n">
-        <v>229794</v>
+        <v>6226</v>
       </c>
       <c r="H6" t="n">
-        <v>115695</v>
+        <v>8689</v>
       </c>
       <c r="I6" t="n">
-        <v>9979</v>
+        <v>80</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>80799</v>
+        <v>25191</v>
       </c>
       <c r="E7" t="n">
-        <v>502867</v>
+        <v>97329</v>
       </c>
       <c r="F7" t="n">
-        <v>1220803</v>
+        <v>153903</v>
       </c>
       <c r="G7" t="n">
-        <v>475279</v>
+        <v>63831</v>
       </c>
       <c r="H7" t="n">
-        <v>3613783</v>
+        <v>171667</v>
       </c>
       <c r="I7" t="n">
-        <v>232284</v>
+        <v>1073</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>6816</v>
+        <v>2735</v>
       </c>
       <c r="E8" t="n">
-        <v>52474</v>
+        <v>12660</v>
       </c>
       <c r="F8" t="n">
-        <v>120508</v>
+        <v>27067</v>
       </c>
       <c r="G8" t="n">
-        <v>71983</v>
+        <v>16992</v>
       </c>
       <c r="H8" t="n">
-        <v>765634</v>
+        <v>131265</v>
       </c>
       <c r="I8" t="n">
-        <v>1304941</v>
+        <v>3331</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
